--- a/data/2025/05-bihor/26564-oradea/budget_file.xlsx
+++ b/data/2025/05-bihor/26564-oradea/budget_file.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>07.02 trim2: parent 49.200,00 != sum(children) 91.800,00 (4 children); 07.02 est2027: parent 154.448,70 != sum(children) 279.917,40 (4 children); 07.02 trim1: parent 36.155,00 != sum(children) 60.485,00 (4 children); 07.02 total: parent 147.900,00 != sum(children) 268.200,00 (4 children); 07.02 est2028: parent 154.098,00 != sum(children) 279.296,00 (4 children); 07.02 trim3: parent 45.445,00 != sum(children) 85.015,00 (4 children); 07.02 trim4: parent 17.100,00 != sum(children) 30.900,00 (4 children)</t>
+          <t>07.02 trim3: parent 45.445,00 != sum(children) 85.015,00 (4 children); 07.02 est2028: parent 154.098,00 != sum(children) 279.296,00 (4 children); 07.02 total: parent 147.900,00 != sum(children) 268.200,00 (4 children); 07.02 trim1: parent 36.155,00 != sum(children) 60.485,00 (4 children); 07.02 est2027: parent 154.448,70 != sum(children) 279.917,40 (4 children); 07.02 trim4: parent 17.100,00 != sum(children) 30.900,00 (4 children); 07.02 trim2: parent 49.200,00 != sum(children) 91.800,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -1390,48 +1390,55 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>11.02</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>SUME DEFALCATE DIN TVA</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="5" t="n">
         <v>140548.53</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="5" t="n">
         <v>36487</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" s="5" t="n">
         <v>36233</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="J21" s="5" t="n">
         <v>33845</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="5" t="n">
         <v>33983.53</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="5" t="n">
         <v>144746.13</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="5" t="n">
         <v>148516.52</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>11.02 trim3: parent 33.845,00 != sum(children) 33.018,00 (3 children); 11.02 est2028: parent 148.516,52 != sum(children) 147.710,52 (3 children); 11.02 total: parent 140.548,53 != sum(children) 137.368,53 (3 children); 11.02 trim1: parent 36.487,00 != sum(children) 35.534,00 (3 children); 11.02 est2027: parent 144.746,13 != sum(children) 143.986,13 (3 children); 11.02 trim4: parent 33.983,53 != sum(children) 33.283,53 (3 children); 11.02 trim2: parent 36.233,00 != sum(children) 35.533,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -1500,30 +1507,16 @@
           <t>revenue</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>3180</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>953</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>700</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>827</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>700</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>760</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>806</v>
-      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2657,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>36.02 trim2: parent 31.952,78 != sum(children) 9.500,00 (2 children); 36.02 est2027: parent 87.356,57 != sum(children) 30.352,16 (2 children); 36.02 trim1: parent 9.889,07 != sum(children) 1.300,00 (2 children); 36.02 total: parent 85.142,85 != sum(children) 29.583,00 (2 children); 36.02 est2028: parent 87.186,28 != sum(children) 30.292,99 (2 children); 36.02 trim3: parent 27.788,00 != sum(children) 10.500,00 (2 children); 36.02 trim4: parent 15.513,00 != sum(children) 8.283,00 (2 children)</t>
+          <t>36.02 trim3: parent 27.788,00 != sum(children) 10.500,00 (2 children); 36.02 est2028: parent 87.186,28 != sum(children) 30.292,99 (2 children); 36.02 total: parent 85.142,85 != sum(children) 29.583,00 (2 children); 36.02 trim1: parent 9.889,07 != sum(children) 1.300,00 (2 children); 36.02 est2027: parent 87.356,57 != sum(children) 30.352,16 (2 children); 36.02 trim4: parent 15.513,00 != sum(children) 8.283,00 (2 children); 36.02 trim2: parent 31.952,78 != sum(children) 9.500,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3511,7 @@
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>42.02.89 trim2: parent 76.097,50 != sum(children) 62.138,27 (2 children); 42.02.89 trim1: parent 65.499,92 != sum(children) 55.099,92 (2 children); 42.02.89 total: parent 288.518,44 != sum(children) 243.443,98 (2 children); 42.02.89 trim3: parent 76.285,09 != sum(children) 65.538,64 (2 children); 42.02.89 trim4: parent 70.635,93 != sum(children) 60.667,15 (2 children)</t>
+          <t>42.02.89 trim3: parent 76.285,09 != sum(children) 65.538,64 (2 children); 42.02.89 total: parent 288.518,44 != sum(children) 243.443,98 (2 children); 42.02.89 trim1: parent 65.499,92 != sum(children) 55.099,92 (2 children); 42.02.89 trim4: parent 70.635,93 != sum(children) 60.667,15 (2 children); 42.02.89 trim2: parent 76.097,50 != sum(children) 62.138,27 (2 children)</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4306,7 @@
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>50.02 trim2: parent 812.224,86 != sum(children) 133.035,68 (3 children); 50.02 est2027: parent 1.252.122,26 != sum(children) 325.235,16 (3 children); 50.02 trim1: parent 424.897,27 != sum(children) 146.740,65 (3 children); 50.02 total: parent 2.532.346,92 != sum(children) 439.188,61 (3 children); 50.02 est2028: parent 1.275.702,68 != sum(children) 353.333,21 (3 children); 50.02 trim3: parent 698.524,10 != sum(children) 104.549,12 (3 children); 50.02 trim4: parent 596.700,69 != sum(children) 54.863,16 (3 children)</t>
+          <t>50.02 trim3: parent 698.524,10 != sum(children) 104.549,12 (3 children); 50.02 est2028: parent 1.275.702,68 != sum(children) 353.333,21 (3 children); 50.02 total: parent 2.532.346,92 != sum(children) 439.188,61 (3 children); 50.02 trim1: parent 424.897,27 != sum(children) 146.740,65 (3 children); 50.02 est2027: parent 1.252.122,26 != sum(children) 325.235,16 (3 children); 50.02 trim4: parent 596.700,69 != sum(children) 54.863,16 (3 children); 50.02 trim2: parent 812.224,86 != sum(children) 133.035,68 (3 children)</t>
         </is>
       </c>
     </row>
@@ -5383,48 +5376,55 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>AUTORITATI PUBLICE SI ACTIUNI EXTERNE</t>
         </is>
       </c>
-      <c r="E110" t="n">
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G110" s="3" t="n">
+      <c r="G110" s="5" t="n">
         <v>106710.03</v>
       </c>
-      <c r="H110" s="3" t="n">
+      <c r="H110" s="5" t="n">
         <v>21488.71</v>
       </c>
-      <c r="I110" s="3" t="n">
+      <c r="I110" s="5" t="n">
         <v>28943.41</v>
       </c>
-      <c r="J110" s="3" t="n">
+      <c r="J110" s="5" t="n">
         <v>30191</v>
       </c>
-      <c r="K110" s="3" t="n">
+      <c r="K110" s="5" t="n">
         <v>26086.91</v>
       </c>
-      <c r="L110" s="3" t="n">
+      <c r="L110" s="5" t="n">
         <v>92410.19</v>
       </c>
-      <c r="M110" s="3" t="n">
+      <c r="M110" s="5" t="n">
         <v>92230.05</v>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>51.02 trim3: parent 30.191,00 != sum(children) 3.495,00 (2 children); 51.02 est2028: parent 92.230,05 != sum(children) 5.916,07 (2 children); 51.02 total: parent 106.710,03 != sum(children) 5.562,12 (2 children); 51.02 trim1: parent 21.488,71 != sum(children) -30,29 (2 children); 51.02 est2027: parent 92.410,19 != sum(children) 5.927,62 (2 children); 51.02 trim4: parent 26.086,91 != sum(children) 900,00 (2 children); 51.02 trim2: parent 28.943,41 != sum(children) 1.197,41 (2 children)</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>20 trim2: parent 4.098,00 != sum(children) 3.948,00 (9 children); 20 trim1: parent 4.019,00 != sum(children) 3.849,00 (9 children); 20 total: parent 15.911,00 != sum(children) 15.411,00 (9 children); 20 trim3: parent 4.039,00 != sum(children) 3.889,00 (9 children); 20 trim4: parent 3.755,00 != sum(children) 3.725,00 (9 children)</t>
+          <t>20 trim3: parent 4.039,00 != sum(children) 3.889,00 (9 children); 20 total: parent 15.911,00 != sum(children) 15.411,00 (9 children); 20 trim1: parent 4.019,00 != sum(children) 3.849,00 (9 children); 20 trim4: parent 3.755,00 != sum(children) 3.725,00 (9 children); 20 trim2: parent 4.098,00 != sum(children) 3.948,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -7872,48 +7872,55 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="4" t="inlineStr">
         <is>
           <t>54.02</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="B164" s="4" t="n"/>
+      <c r="C164" s="4" t="inlineStr">
         <is>
           <t>ALTE SERVICII PUBLICE GENERALE</t>
         </is>
       </c>
-      <c r="E164" t="n">
+      <c r="D164" s="4" t="n"/>
+      <c r="E164" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G164" s="3" t="n">
+      <c r="G164" s="5" t="n">
         <v>9629</v>
       </c>
-      <c r="H164" s="3" t="n">
+      <c r="H164" s="5" t="n">
         <v>6234</v>
       </c>
-      <c r="I164" s="3" t="n">
+      <c r="I164" s="5" t="n">
         <v>1361.8</v>
       </c>
-      <c r="J164" s="3" t="n">
+      <c r="J164" s="5" t="n">
         <v>1067</v>
       </c>
-      <c r="K164" s="3" t="n">
+      <c r="K164" s="5" t="n">
         <v>966.2</v>
       </c>
-      <c r="L164" s="3" t="n">
+      <c r="L164" s="5" t="n">
         <v>4749.35</v>
       </c>
-      <c r="M164" s="3" t="n">
+      <c r="M164" s="5" t="n">
         <v>4740.1</v>
       </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O164" s="4" t="inlineStr">
+        <is>
+          <t>54.02 est2028: parent 4.740,10 != sum(children) 51,20 (1 children); 54.02 total: parent 9.629,00 != sum(children) 50,00 (1 children); 54.02 trim1: parent 6.234,00 != sum(children) 30,00 (1 children); 54.02 est2027: parent 4.749,35 != sum(children) 51,30 (1 children); 54.02 trim2: parent 1.361,80 != sum(children) 20,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8077,7 @@
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>10.01 trim2: parent 1.013,00 != sum(children) 985,00 (4 children); 10.01 trim1: parent 1.021,00 != sum(children) 993,00 (4 children); 10.01 total: parent 3.959,20 != sum(children) 3.847,20 (4 children); 10.01 trim3: parent 1.006,00 != sum(children) 978,00 (4 children); 10.01 trim4: parent 919,20 != sum(children) 891,20 (4 children)</t>
+          <t>10.01 trim3: parent 1.006,00 != sum(children) 978,00 (4 children); 10.01 total: parent 3.959,20 != sum(children) 3.847,20 (4 children); 10.01 trim1: parent 1.021,00 != sum(children) 993,00 (4 children); 10.01 trim4: parent 919,20 != sum(children) 891,20 (4 children); 10.01 trim2: parent 1.013,00 != sum(children) 985,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -9281,20 +9288,14 @@
       <c r="H194" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="I194" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I194" s="3" t="n"/>
       <c r="J194" s="3" t="n"/>
       <c r="K194" s="3" t="n"/>
-      <c r="L194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M194" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="L194" s="3" t="n"/>
+      <c r="M194" s="3" t="n"/>
       <c r="N194" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -11566,48 +11567,55 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="4" t="inlineStr">
         <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="B245" s="4" t="n"/>
+      <c r="C245" s="4" t="inlineStr">
         <is>
           <t>INVATAMANT</t>
         </is>
       </c>
-      <c r="E245" t="n">
+      <c r="D245" s="4" t="n"/>
+      <c r="E245" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F245" t="inlineStr">
+      <c r="F245" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G245" s="3" t="n">
+      <c r="G245" s="5" t="n">
         <v>305894.81</v>
       </c>
-      <c r="H245" s="3" t="n">
+      <c r="H245" s="5" t="n">
         <v>24615.8</v>
       </c>
-      <c r="I245" s="3" t="n">
+      <c r="I245" s="5" t="n">
         <v>85468.8</v>
       </c>
-      <c r="J245" s="3" t="n">
+      <c r="J245" s="5" t="n">
         <v>100483.31</v>
       </c>
-      <c r="K245" s="3" t="n">
+      <c r="K245" s="5" t="n">
         <v>95326.89999999999</v>
       </c>
-      <c r="L245" s="3" t="n">
+      <c r="L245" s="5" t="n">
         <v>93482.03</v>
       </c>
-      <c r="M245" s="3" t="n">
+      <c r="M245" s="5" t="n">
         <v>93409.53999999999</v>
       </c>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N245" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O245" s="4" t="inlineStr">
+        <is>
+          <t>65.02 trim3: parent 100.483,31 != sum(children) 1.768,21 (2 children); 65.02 est2028: parent 93.409,54 != sum(children) 6.092,96 (2 children); 65.02 total: parent 305.894,81 != sum(children) 5.934,89 (2 children); 65.02 trim1: parent 24.615,80 != sum(children) 186,68 (2 children); 65.02 est2027: parent 93.482,03 != sum(children) 6.104,85 (2 children); 65.02 trim4: parent 95.326,90 != sum(children) 1.721,00 (2 children); 65.02 trim2: parent 85.468,80 != sum(children) 2.259,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -15187,15 +15195,11 @@
       <c r="K323" s="3" t="n">
         <v>389</v>
       </c>
-      <c r="L323" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M323" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="L323" s="3" t="n"/>
+      <c r="M323" s="3" t="n"/>
       <c r="N323" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -15334,48 +15338,55 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
+      <c r="A327" s="4" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
+      <c r="B327" s="4" t="n"/>
+      <c r="C327" s="4" t="inlineStr">
         <is>
           <t>SANATATE</t>
         </is>
       </c>
-      <c r="E327" t="n">
+      <c r="D327" s="4" t="n"/>
+      <c r="E327" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F327" t="inlineStr">
+      <c r="F327" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G327" s="3" t="n">
+      <c r="G327" s="5" t="n">
         <v>711269.55</v>
       </c>
-      <c r="H327" s="3" t="n">
+      <c r="H327" s="5" t="n">
         <v>7153</v>
       </c>
-      <c r="I327" s="3" t="n">
+      <c r="I327" s="5" t="n">
         <v>273726.3</v>
       </c>
-      <c r="J327" s="3" t="n">
+      <c r="J327" s="5" t="n">
         <v>248278.31</v>
       </c>
-      <c r="K327" s="3" t="n">
+      <c r="K327" s="5" t="n">
         <v>182111.94</v>
       </c>
-      <c r="L327" s="3" t="n">
+      <c r="L327" s="5" t="n">
         <v>62026.83</v>
       </c>
-      <c r="M327" s="3" t="n">
+      <c r="M327" s="5" t="n">
         <v>61905.93</v>
       </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N327" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O327" s="4" t="inlineStr">
+        <is>
+          <t>66.02 trim3: parent 248.278,31 != sum(children) 1.000,00 (2 children); 66.02 est2028: parent 61.905,93 != sum(children) 31.072,13 (2 children); 66.02 total: parent 711.269,55 != sum(children) 30.343,87 (2 children); 66.02 est2027: parent 62.026,83 != sum(children) 31.132,81 (2 children); 66.02 trim4: parent 182.111,94 != sum(children) 1.855,81 (2 children); 66.02 trim2: parent 273.726,30 != sum(children) 27.488,06 (2 children)</t>
         </is>
       </c>
     </row>
@@ -16511,47 +16522,45 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
+      <c r="A353" s="4" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="4" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="4" t="inlineStr">
         <is>
           <t>TITLUL VIII PROIECTE CU FINANTARE DIN</t>
         </is>
       </c>
-      <c r="E353" t="n">
+      <c r="D353" s="4" t="n"/>
+      <c r="E353" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G353" s="3" t="n">
-        <v>15557.72</v>
-      </c>
-      <c r="H353" s="3" t="n"/>
-      <c r="I353" s="3" t="n">
-        <v>5886.22</v>
-      </c>
-      <c r="J353" s="3" t="n">
-        <v>5600</v>
-      </c>
-      <c r="K353" s="3" t="n">
-        <v>4071.5</v>
-      </c>
-      <c r="L353" s="3" t="n"/>
-      <c r="M353" s="3" t="n"/>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G353" s="5" t="n"/>
+      <c r="H353" s="5" t="n"/>
+      <c r="I353" s="5" t="n"/>
+      <c r="J353" s="5" t="n"/>
+      <c r="K353" s="5" t="n"/>
+      <c r="L353" s="5" t="n"/>
+      <c r="M353" s="5" t="n"/>
+      <c r="N353" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O353" s="4" t="inlineStr">
+        <is>
+          <t>56 trim2: parent 0,00 != sum(children) 5.886,22 (1 children); 56 total: parent 0,00 != sum(children) 15.557,72 (1 children); 56 trim3: parent 0,00 != sum(children) 5.600,00 (1 children); 56 trim4: parent 0,00 != sum(children) 4.071,50 (1 children)</t>
         </is>
       </c>
     </row>
@@ -17852,12 +17861,8 @@
       <c r="I382" s="3" t="n">
         <v>3035.47</v>
       </c>
-      <c r="J382" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K382" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J382" s="3" t="n"/>
+      <c r="K382" s="3" t="n"/>
       <c r="L382" s="3" t="n">
         <v>2352.07</v>
       </c>
@@ -17866,7 +17871,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -17959,7 +17964,7 @@
       </c>
       <c r="O384" s="4" t="inlineStr">
         <is>
-          <t>67.02 trim2: parent 34.411,27 != sum(children) 23.413,27 (3 children); 67.02 est2027: parent 111.589,00 != sum(children) 76.710,07 (3 children); 67.02 trim1: parent 24.066,38 != sum(children) 16.883,73 (3 children); 67.02 total: parent 102.525,23 != sum(children) 68.530,17 (3 children); 67.02 est2028: parent 111.390,99 != sum(children) 76.580,04 (3 children); 67.02 trim3: parent 25.462,29 != sum(children) 16.575,29 (3 children); 67.02 trim4: parent 18.585,29 != sum(children) 11.657,88 (3 children); 67.02 trim2: parent 34.411,27 != sum(children) 7.007,62 (1 children); 67.02 est2027: parent 111.589,00 != sum(children) 21.365,87 (1 children); 67.02 trim1: parent 24.066,38 != sum(children) 782,65 (1 children); 67.02 total: parent 102.525,23 != sum(children) 11.077,84 (1 children); 67.02 est2028: parent 111.390,99 != sum(children) 21.343,71 (1 children); 67.02 trim3: parent 25.462,29 != sum(children) 2.643,66 (1 children); 67.02 trim4: parent 18.585,29 != sum(children) 643,91 (1 children)</t>
+          <t>67.02 trim3: parent 25.462,29 != sum(children) 16.575,29 (3 children); 67.02 est2028: parent 111.390,99 != sum(children) 76.580,04 (3 children); 67.02 total: parent 102.525,23 != sum(children) 68.530,17 (3 children); 67.02 trim1: parent 24.066,38 != sum(children) 16.883,73 (3 children); 67.02 est2027: parent 111.589,00 != sum(children) 76.710,07 (3 children); 67.02 trim4: parent 18.585,29 != sum(children) 11.657,88 (3 children); 67.02 trim2: parent 34.411,27 != sum(children) 23.413,27 (3 children); 67.02 trim3: parent 25.462,29 != sum(children) 2.643,66 (1 children); 67.02 est2028: parent 111.390,99 != sum(children) 21.343,71 (1 children); 67.02 total: parent 102.525,23 != sum(children) 11.077,84 (1 children); 67.02 trim1: parent 24.066,38 != sum(children) 782,65 (1 children); 67.02 est2027: parent 111.589,00 != sum(children) 21.365,87 (1 children); 67.02 trim4: parent 18.585,29 != sum(children) 643,91 (1 children); 67.02 trim2: parent 34.411,27 != sum(children) 7.007,62 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19065,7 @@
       </c>
       <c r="O407" s="4" t="inlineStr">
         <is>
-          <t>56.48 trim1: parent 2.216,55 != sum(children) 1.282,16 (2 children); 56.48 total: parent 2.216,55 != sum(children) 1.282,16 (2 children)</t>
+          <t>56.48 total: parent 2.216,55 != sum(children) 1.282,16 (2 children); 56.48 trim1: parent 2.216,55 != sum(children) 1.282,16 (2 children)</t>
         </is>
       </c>
     </row>
@@ -20292,7 +20297,7 @@
       </c>
       <c r="O435" s="4" t="inlineStr">
         <is>
-          <t>68.02 trim2: parent 25.074,00 != sum(children) 20.335,00 (3 children); 68.02 est2027: parent 96.233,45 != sum(children) 81.516,44 (3 children); 68.02 trim1: parent 23.891,64 != sum(children) 20.054,72 (3 children); 68.02 total: parent 91.558,86 != sum(children) 77.250,94 (3 children); 68.02 est2028: parent 98.592,34 != sum(children) 83.904,03 (3 children); 68.02 trim3: parent 22.676,00 != sum(children) 18.549,00 (3 children); 68.02 trim4: parent 19.917,22 != sum(children) 18.312,22 (3 children); 68.02 est2027: parent 96.233,45 != sum(children) 282,15 (2 children); 68.02 trim1: parent 23.891,64 != sum(children) -57,42 (2 children); 68.02 total: parent 91.558,86 != sum(children) 217,58 (2 children); 68.02 est2028: parent 98.592,34 != sum(children) 281,60 (2 children); 68.02 trim2: parent 25.074,00 != sum(children) 275,00 (2 children)</t>
+          <t>68.02 trim3: parent 22.676,00 != sum(children) 18.549,00 (3 children); 68.02 est2028: parent 98.592,34 != sum(children) 83.904,03 (3 children); 68.02 total: parent 91.558,86 != sum(children) 77.250,94 (3 children); 68.02 trim1: parent 23.891,64 != sum(children) 20.054,72 (3 children); 68.02 est2027: parent 96.233,45 != sum(children) 81.516,44 (3 children); 68.02 trim4: parent 19.917,22 != sum(children) 18.312,22 (3 children); 68.02 trim2: parent 25.074,00 != sum(children) 20.335,00 (3 children); 68.02 est2028: parent 98.592,34 != sum(children) 281,60 (2 children); 68.02 total: parent 91.558,86 != sum(children) 217,58 (2 children); 68.02 trim1: parent 23.891,64 != sum(children) -57,42 (2 children); 68.02 est2027: parent 96.233,45 != sum(children) 282,15 (2 children); 68.02 trim2: parent 25.074,00 != sum(children) 275,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21039,7 @@
       </c>
       <c r="O451" s="4" t="inlineStr">
         <is>
-          <t>20 trim2: parent 1.217,00 != sum(children) 1.214,00 (9 children); 20 trim1: parent 1.157,00 != sum(children) 1.155,00 (9 children); 20 total: parent 3.508,00 != sum(children) 3.503,00 (9 children)</t>
+          <t>20 total: parent 3.508,00 != sum(children) 3.503,00 (9 children); 20 trim1: parent 1.157,00 != sum(children) 1.155,00 (9 children); 20 trim2: parent 1.217,00 != sum(children) 1.214,00 (9 children)</t>
         </is>
       </c>
     </row>
@@ -23268,48 +23273,55 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
+      <c r="A502" s="4" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
+      <c r="B502" s="4" t="n"/>
+      <c r="C502" s="4" t="inlineStr">
         <is>
           <t>LOCUINTE, SERVICII SI DEZVOLTARE</t>
         </is>
       </c>
-      <c r="E502" t="n">
+      <c r="D502" s="4" t="n"/>
+      <c r="E502" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="F502" t="inlineStr">
+      <c r="F502" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G502" s="3" t="n">
+      <c r="G502" s="5" t="n">
         <v>250922.28</v>
       </c>
-      <c r="H502" s="3" t="n">
+      <c r="H502" s="5" t="n">
         <v>62963.26</v>
       </c>
-      <c r="I502" s="3" t="n">
+      <c r="I502" s="5" t="n">
         <v>77899.97</v>
       </c>
-      <c r="J502" s="3" t="n">
+      <c r="J502" s="5" t="n">
         <v>46627.57</v>
       </c>
-      <c r="K502" s="3" t="n">
+      <c r="K502" s="5" t="n">
         <v>63431.48</v>
       </c>
-      <c r="L502" s="3" t="n">
+      <c r="L502" s="5" t="n">
         <v>188708.85</v>
       </c>
-      <c r="M502" s="3" t="n">
+      <c r="M502" s="5" t="n">
         <v>203100.93</v>
       </c>
-      <c r="N502" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N502" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O502" s="4" t="inlineStr">
+        <is>
+          <t>70.02 trim3: parent 46.627,57 != sum(children) 4.635,63 (3 children); 70.02 est2028: parent 203.100,93 != sum(children) 127.427,59 (3 children); 70.02 total: parent 250.922,28 != sum(children) 106.054,76 (3 children); 70.02 trim1: parent 62.963,26 != sum(children) 37.557,42 (3 children); 70.02 est2027: parent 188.708,85 != sum(children) 112.887,69 (3 children); 70.02 trim4: parent 63.431,48 != sum(children) 26.182,63 (3 children); 70.02 trim2: parent 77.899,97 != sum(children) 37.679,08 (3 children)</t>
         </is>
       </c>
     </row>
@@ -25775,9 +25787,7 @@
       <c r="G557" s="3" t="n">
         <v>51888.62</v>
       </c>
-      <c r="H557" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="H557" s="3" t="n"/>
       <c r="I557" s="3" t="n">
         <v>5288.62</v>
       </c>
@@ -25795,7 +25805,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -26028,48 +26038,55 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
+      <c r="A563" s="4" t="inlineStr">
         <is>
           <t>74.02</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr">
+      <c r="B563" s="4" t="n"/>
+      <c r="C563" s="4" t="inlineStr">
         <is>
           <t>PROTECTIA MEDIULUI</t>
         </is>
       </c>
-      <c r="E563" t="n">
+      <c r="D563" s="4" t="n"/>
+      <c r="E563" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="F563" t="inlineStr">
+      <c r="F563" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G563" s="3" t="n">
+      <c r="G563" s="5" t="n">
         <v>76185.8</v>
       </c>
-      <c r="H563" s="3" t="n">
+      <c r="H563" s="5" t="n">
         <v>14865.17</v>
       </c>
-      <c r="I563" s="3" t="n">
+      <c r="I563" s="5" t="n">
         <v>39362.79</v>
       </c>
-      <c r="J563" s="3" t="n">
+      <c r="J563" s="5" t="n">
         <v>11827</v>
       </c>
-      <c r="K563" s="3" t="n">
+      <c r="K563" s="5" t="n">
         <v>10130.84</v>
       </c>
-      <c r="L563" s="3" t="n">
+      <c r="L563" s="5" t="n">
         <v>49934.42</v>
       </c>
-      <c r="M563" s="3" t="n">
+      <c r="M563" s="5" t="n">
         <v>49837.09</v>
       </c>
-      <c r="N563" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N563" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O563" s="4" t="inlineStr">
+        <is>
+          <t>74.02 est2028: parent 49.837,09 != sum(children) 2.600,96 (2 children); 74.02 total: parent 76.185,80 != sum(children) 2.480,98 (2 children); 74.02 trim1: parent 14.865,17 != sum(children) -19,02 (2 children); 74.02 est2027: parent 49.934,42 != sum(children) 2.606,04 (2 children); 74.02 trim2: parent 39.362,79 != sum(children) 2.500,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -26611,7 +26628,7 @@
       </c>
       <c r="O575" s="4" t="inlineStr">
         <is>
-          <t>61 trim1: parent 2.500,00 != sum(children) 400,00 (1 children); 61 total: parent 27.575,79 != sum(children) 4.402,88 (1 children); 61 trim2: parent 25.075,79 != sum(children) 4.002,88 (1 children)</t>
+          <t>61 trim2: parent 25.075,79 != sum(children) 4.002,88 (1 children); 61 total: parent 27.575,79 != sum(children) 4.402,88 (1 children); 61 trim1: parent 2.500,00 != sum(children) 400,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -27245,9 +27262,7 @@
       <c r="G590" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H590" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="H590" s="3" t="n"/>
       <c r="I590" s="3" t="n">
         <v>15</v>
       </c>
@@ -27261,7 +27276,7 @@
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -27360,7 +27375,7 @@
       </c>
       <c r="O592" s="4" t="inlineStr">
         <is>
-          <t>80.02 trim2: parent 4.049,31 != sum(children) 224.343,27 (1 children); 80.02 est2027: parent 831,06 != sum(children) 509.143,18 (1 children); 80.02 trim1: parent 17,00 != sum(children) 235.276,56 (1 children); 80.02 total: parent 11.659,31 != sum(children) 823.479,26 (1 children); 80.02 est2028: parent 829,44 != sum(children) 522.083,79 (1 children); 80.02 trim3: parent 3.900,00 != sum(children) 207.229,62 (1 children); 80.02 trim4: parent 3.693,00 != sum(children) 156.629,81 (1 children); 80.02 trim2: parent 4.049,31 != sum(children) 200,00 (1 children); 80.02 est2027: parent 831,06 != sum(children) 813,62 (1 children); 80.02 total: parent 11.659,31 != sum(children) 793,00 (1 children); 80.02 est2028: parent 829,44 != sum(children) 812,03 (1 children); 80.02 trim3: parent 3.900,00 != sum(children) 400,00 (1 children); 80.02 trim4: parent 3.693,00 != sum(children) 193,00 (1 children)</t>
+          <t>80.02 trim3: parent 3.900,00 != sum(children) 207.229,62 (1 children); 80.02 est2028: parent 829,44 != sum(children) 522.083,79 (1 children); 80.02 total: parent 11.659,31 != sum(children) 823.479,26 (1 children); 80.02 trim1: parent 17,00 != sum(children) 235.276,56 (1 children); 80.02 est2027: parent 831,06 != sum(children) 509.143,18 (1 children); 80.02 trim4: parent 3.693,00 != sum(children) 156.629,81 (1 children); 80.02 trim2: parent 4.049,31 != sum(children) 224.343,27 (1 children); 80.02 trim3: parent 3.900,00 != sum(children) 400,00 (1 children); 80.02 est2028: parent 829,44 != sum(children) 812,03 (1 children); 80.02 total: parent 11.659,31 != sum(children) 793,00 (1 children); 80.02 est2027: parent 831,06 != sum(children) 813,62 (1 children); 80.02 trim4: parent 3.693,00 != sum(children) 193,00 (1 children); 80.02 trim2: parent 4.049,31 != sum(children) 200,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -27914,48 +27929,55 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="inlineStr">
+      <c r="A605" s="4" t="inlineStr">
         <is>
           <t>81.02</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="B605" s="4" t="n"/>
+      <c r="C605" s="4" t="inlineStr">
         <is>
           <t>COMBUSTIBILI SI ENERGIE</t>
         </is>
       </c>
-      <c r="E605" t="n">
+      <c r="D605" s="4" t="n"/>
+      <c r="E605" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F605" t="inlineStr">
+      <c r="F605" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G605" s="3" t="n">
+      <c r="G605" s="5" t="n">
         <v>312794.97</v>
       </c>
-      <c r="H605" s="3" t="n">
+      <c r="H605" s="5" t="n">
         <v>111864.72</v>
       </c>
-      <c r="I605" s="3" t="n">
+      <c r="I605" s="5" t="n">
         <v>69087.25</v>
       </c>
-      <c r="J605" s="3" t="n">
+      <c r="J605" s="5" t="n">
         <v>93025.5</v>
       </c>
-      <c r="K605" s="3" t="n">
+      <c r="K605" s="5" t="n">
         <v>38817.5</v>
       </c>
-      <c r="L605" s="3" t="n">
+      <c r="L605" s="5" t="n">
         <v>160788.57</v>
       </c>
-      <c r="M605" s="3" t="n">
+      <c r="M605" s="5" t="n">
         <v>160514.14</v>
       </c>
-      <c r="N605" t="inlineStr">
-        <is>
-          <t>digital</t>
+      <c r="N605" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O605" s="4" t="inlineStr">
+        <is>
+          <t>81.02 trim3: parent 93.025,50 != sum(children) 61.537,50 (3 children); 81.02 est2028: parent 160.514,14 != sum(children) 31.996,80 (3 children); 81.02 total: parent 312.794,97 != sum(children) 177.524,13 (3 children); 81.02 trim1: parent 111.864,72 != sum(children) 94.395,79 (3 children); 81.02 est2027: parent 160.788,57 != sum(children) 32.000,70 (3 children); 81.02 trim4: parent 38.817,50 != sum(children) 987,50 (3 children); 81.02 trim2: parent 69.087,25 != sum(children) 20.603,34 (3 children)</t>
         </is>
       </c>
     </row>
@@ -29479,7 +29501,7 @@
       </c>
       <c r="O638" s="4" t="inlineStr">
         <is>
-          <t>84.02 total: parent 499.024,98 != sum(children) 2.000,00 (1 children); 84.02 trim3: parent 110.304,12 != sum(children) 1.000,00 (1 children); 84.02 trim2: parent 151.206,71 != sum(children) 1.000,00 (1 children); 84.02 trim2: parent 151.206,71 != sum(children) 33.481,07 (2 children); 84.02 est2027: parent 347.523,55 != sum(children) 111.036,41 (2 children); 84.02 trim1: parent 123.394,84 != sum(children) 13.894,84 (2 children); 84.02 total: parent 499.024,98 != sum(children) 98.149,34 (2 children); 84.02 est2028: parent 360.740,21 != sum(children) 124.714,06 (2 children); 84.02 trim3: parent 110.304,12 != sum(children) 28.394,12 (2 children); 84.02 trim4: parent 114.119,31 != sum(children) 22.379,31 (2 children)</t>
+          <t>84.02 trim2: parent 151.206,71 != sum(children) 1.000,00 (1 children); 84.02 total: parent 499.024,98 != sum(children) 2.000,00 (1 children); 84.02 trim3: parent 110.304,12 != sum(children) 1.000,00 (1 children); 84.02 trim3: parent 110.304,12 != sum(children) 28.394,12 (2 children); 84.02 est2028: parent 360.740,21 != sum(children) 124.714,06 (2 children); 84.02 total: parent 499.024,98 != sum(children) 98.149,34 (2 children); 84.02 trim1: parent 123.394,84 != sum(children) 13.894,84 (2 children); 84.02 est2027: parent 347.523,55 != sum(children) 111.036,41 (2 children); 84.02 trim4: parent 114.119,31 != sum(children) 22.379,31 (2 children); 84.02 trim2: parent 151.206,71 != sum(children) 33.481,07 (2 children)</t>
         </is>
       </c>
     </row>
@@ -30132,49 +30154,45 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr">
+      <c r="A653" s="4" t="inlineStr">
         <is>
           <t>56.48</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B653" s="4" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
+      <c r="C653" s="4" t="inlineStr">
         <is>
           <t>Programe finantate din Fondul</t>
         </is>
       </c>
-      <c r="E653" t="n">
+      <c r="D653" s="4" t="n"/>
+      <c r="E653" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F653" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G653" s="3" t="n">
-        <v>113474.29</v>
-      </c>
-      <c r="H653" s="3" t="n">
-        <v>16040</v>
-      </c>
-      <c r="I653" s="3" t="n">
-        <v>30334.29</v>
-      </c>
-      <c r="J653" s="3" t="n">
-        <v>25060</v>
-      </c>
-      <c r="K653" s="3" t="n">
-        <v>42040</v>
-      </c>
-      <c r="L653" s="3" t="n"/>
-      <c r="M653" s="3" t="n"/>
-      <c r="N653" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
+      <c r="F653" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G653" s="5" t="n"/>
+      <c r="H653" s="5" t="n"/>
+      <c r="I653" s="5" t="n"/>
+      <c r="J653" s="5" t="n"/>
+      <c r="K653" s="5" t="n"/>
+      <c r="L653" s="5" t="n"/>
+      <c r="M653" s="5" t="n"/>
+      <c r="N653" s="4" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="O653" s="4" t="inlineStr">
+        <is>
+          <t>56.48 trim3: parent 0,00 != sum(children) 25.060,00 (3 children); 56.48 total: parent 0,00 != sum(children) 113.474,29 (3 children); 56.48 trim1: parent 0,00 != sum(children) 16.040,00 (3 children); 56.48 trim4: parent 0,00 != sum(children) 42.040,00 (3 children); 56.48 trim2: parent 0,00 != sum(children) 30.334,29 (3 children)</t>
         </is>
       </c>
     </row>
@@ -30338,17 +30356,13 @@
       <c r="I657" s="3" t="n">
         <v>4493.57</v>
       </c>
-      <c r="J657" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K657" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J657" s="3" t="n"/>
+      <c r="K657" s="3" t="n"/>
       <c r="L657" s="3" t="n"/>
       <c r="M657" s="3" t="n"/>
       <c r="N657" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>digital</t>
         </is>
       </c>
     </row>
@@ -62499,7 +62513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F264"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -62545,12 +62559,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -62563,24 +62577,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 est2027: still inconsistent — UNRESOLVED</t>
+          <t>07.02 trim3: parent 45.445,00 != sum(children) 85.015,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -62598,19 +62612,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 est2028: still inconsistent — UNRESOLVED</t>
+          <t>07.02 est2028: parent 154.098,00 != sum(children) 279.296,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -62628,19 +62642,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 total: still inconsistent — UNRESOLVED</t>
+          <t>07.02 total: parent 147.900,00 != sum(children) 268.200,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -62658,19 +62672,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>07.02 trim1: parent 36.155,00 != sum(children) 60.485,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -62683,24 +62697,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>07.02 est2027: parent 154.448,70 != sum(children) 279.917,40 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -62713,24 +62727,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>07.02 trim4: parent 17.100,00 != sum(children) 30.900,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -62743,24 +62757,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>07.02 trim2: parent 49.200,00 != sum(children) 91.800,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -62768,29 +62782,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>07.02.02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 est2027: sum now consistent — applied</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -62803,24 +62812,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 est2028: sum now consistent — applied</t>
+          <t>11.02 trim3: parent 33.845,00 != sum(children) 33.018,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -62833,24 +62842,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 total: sum now consistent — applied</t>
+          <t>11.02 est2028: parent 148.516,52 != sum(children) 147.710,52 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -62863,24 +62872,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 trim1: sum now consistent — applied</t>
+          <t>11.02 total: parent 140.548,53 != sum(children) 137.368,53 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -62893,24 +62902,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 trim2: sum now consistent — applied</t>
+          <t>11.02 trim1: parent 36.487,00 != sum(children) 35.534,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -62923,24 +62932,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 trim3: sum now consistent — applied</t>
+          <t>11.02 est2027: parent 144.746,13 != sum(children) 143.986,13 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -62958,49 +62967,49 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 11.02 trim4: sum now consistent — applied</t>
+          <t>11.02 trim4: parent 33.983,53 != sum(children) 33.283,53 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 36.02 est2027: still inconsistent — UNRESOLVED</t>
+          <t>11.02 trim2: parent 36.233,00 != sum(children) 35.533,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -63013,24 +63022,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 36.02 est2028: still inconsistent — UNRESOLVED</t>
+          <t>36.02 trim3: parent 27.788,00 != sum(children) 10.500,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -63043,24 +63052,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 36.02 total: still inconsistent — UNRESOLVED</t>
+          <t>36.02 est2028: parent 87.186,28 != sum(children) 30.292,99 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -63073,24 +63082,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 36.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>36.02 total: parent 85.142,85 != sum(children) 29.583,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -63103,24 +63112,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 36.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>36.02 trim1: parent 9.889,07 != sum(children) 1.300,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -63133,24 +63142,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 36.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>36.02 est2027: parent 87.356,57 != sum(children) 30.352,16 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -63168,49 +63177,49 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 36.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>36.02 trim4: parent 15.513,00 != sum(children) 8.283,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>42.02.89</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 42.02.89 total: still inconsistent — UNRESOLVED</t>
+          <t>36.02 trim2: parent 31.952,78 != sum(children) 9.500,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -63223,24 +63232,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 42.02.89 trim1: still inconsistent — UNRESOLVED</t>
+          <t>42.02.89 trim3: parent 76.285,09 != sum(children) 65.538,64 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -63253,24 +63262,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 42.02.89 trim2: still inconsistent — UNRESOLVED</t>
+          <t>42.02.89 total: parent 288.518,44 != sum(children) 243.443,98 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -63283,24 +63292,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 42.02.89 trim3: still inconsistent — UNRESOLVED</t>
+          <t>42.02.89 trim1: parent 65.499,92 != sum(children) 55.099,92 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -63318,49 +63327,49 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 42.02.89 trim4: still inconsistent — UNRESOLVED</t>
+          <t>42.02.89 trim4: parent 70.635,93 != sum(children) 60.667,15 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>42.02.89</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 est2027: sum now consistent — applied</t>
+          <t>42.02.89 trim2: parent 76.097,50 != sum(children) 62.138,27 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -63368,29 +63377,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 est2028: sum now consistent — applied</t>
+          <t>50.02 trim3: parent 698.524,10 != sum(children) 104.549,12 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -63398,29 +63407,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 total: sum now consistent — applied</t>
+          <t>50.02 est2028: parent 1.275.702,68 != sum(children) 353.333,21 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -63428,29 +63437,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 trim1: sum now consistent — applied</t>
+          <t>50.02 total: parent 2.532.346,92 != sum(children) 439.188,61 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -63458,29 +63467,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 trim2: sum now consistent — applied</t>
+          <t>50.02 trim1: parent 424.897,27 != sum(children) 146.740,65 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -63488,29 +63497,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 trim3: sum now consistent — applied</t>
+          <t>50.02 est2027: parent 1.252.122,26 != sum(children) 325.235,16 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -63518,7 +63527,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -63528,177 +63537,177 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 trim4: sum now consistent — applied</t>
+          <t>50.02 trim4: parent 596.700,69 != sum(children) 54.863,16 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LLM re-read 10 rows for 20 total: still inconsistent — UNRESOLVED</t>
+          <t>50.02 trim2: parent 812.224,86 != sum(children) 133.035,68 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LLM re-read 10 rows for 20 trim1: still inconsistent — UNRESOLVED</t>
+          <t>51.02 trim3: parent 30.191,00 != sum(children) 3.495,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LLM re-read 10 rows for 20 trim2: still inconsistent — UNRESOLVED</t>
+          <t>51.02 est2028: parent 92.230,05 != sum(children) 5.916,07 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LLM re-read 10 rows for 20 trim3: still inconsistent — UNRESOLVED</t>
+          <t>51.02 total: parent 106.710,03 != sum(children) 5.562,12 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LLM re-read 10 rows for 20 trim4: still inconsistent — UNRESOLVED</t>
+          <t>51.02 trim1: parent 21.488,71 != sum(children) -30,29 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -63708,207 +63717,207 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 54.02 est2027: sum now consistent — applied</t>
+          <t>51.02 est2027: parent 92.410,19 != sum(children) 5.927,62 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 54.02 est2028: sum now consistent — applied</t>
+          <t>51.02 trim4: parent 26.086,91 != sum(children) 900,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 54.02 total: sum now consistent — applied</t>
+          <t>51.02 trim2: parent 28.943,41 != sum(children) 1.197,41 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 54.02 trim1: sum now consistent — applied</t>
+          <t>20 trim3: parent 4.039,00 != sum(children) 3.889,00 (9 children)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 54.02 trim2: sum now consistent — applied</t>
+          <t>20 total: parent 15.911,00 != sum(children) 15.411,00 (9 children)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 10.01 total: still inconsistent — UNRESOLVED</t>
+          <t>20 trim1: parent 4.019,00 != sum(children) 3.849,00 (9 children)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 10.01 trim1: still inconsistent — UNRESOLVED</t>
+          <t>20 trim4: parent 3.755,00 != sum(children) 3.725,00 (9 children)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -63918,14 +63927,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 10.01 trim2: still inconsistent — UNRESOLVED</t>
+          <t>20 trim2: parent 4.098,00 != sum(children) 3.948,00 (9 children)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -63938,29 +63947,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 10.01 trim3: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -63968,187 +63972,182 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 10.01 trim4: still inconsistent — UNRESOLVED</t>
+          <t>54.02 est2028: parent 4.740,10 != sum(children) 51,20 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 65.02 est2027: sum now consistent — applied</t>
+          <t>54.02 total: parent 9.629,00 != sum(children) 50,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 65.02 est2028: sum now consistent — applied</t>
+          <t>54.02 trim1: parent 6.234,00 != sum(children) 30,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 65.02 total: sum now consistent — applied</t>
+          <t>54.02 est2027: parent 4.749,35 != sum(children) 51,30 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 65.02 trim1: sum now consistent — applied</t>
+          <t>54.02 trim2: parent 1.361,80 != sum(children) 20,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 65.02 trim2: sum now consistent — applied</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -64158,404 +64157,394 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 65.02 trim3: sum now consistent — applied</t>
+          <t>10.01 trim3: parent 1.006,00 != sum(children) 978,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 65.02 trim4: sum now consistent — applied</t>
+          <t>10.01 total: parent 3.959,20 != sum(children) 3.847,20 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 66.02 est2027: sum now consistent — applied</t>
+          <t>10.01 trim1: parent 1.021,00 != sum(children) 993,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 66.02 est2028: sum now consistent — applied</t>
+          <t>10.01 trim4: parent 919,20 != sum(children) 891,20 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 66.02 total: sum now consistent — applied</t>
+          <t>10.01 trim2: parent 1.013,00 != sum(children) 985,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 66.02 trim2: sum now consistent — applied</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 66.02 trim3: sum now consistent — applied</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 66.02 trim4: sum now consistent — applied</t>
+          <t>65.02 trim3: parent 100.483,31 != sum(children) 1.768,21 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 56 total: sum now consistent — applied</t>
+          <t>65.02 est2028: parent 93.409,54 != sum(children) 6.092,96 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 56 trim2: sum now consistent — applied</t>
+          <t>65.02 total: parent 305.894,81 != sum(children) 5.934,89 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 56 trim3: sum now consistent — applied</t>
+          <t>65.02 trim1: parent 24.615,80 != sum(children) 186,68 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 56 trim4: sum now consistent — applied</t>
+          <t>65.02 est2027: parent 93.482,03 != sum(children) 6.104,85 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 est2027: still inconsistent — UNRESOLVED</t>
+          <t>65.02 trim4: parent 95.326,90 != sum(children) 1.721,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 est2028: still inconsistent — UNRESOLVED</t>
+          <t>65.02 trim2: parent 85.468,80 != sum(children) 2.259,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -64564,28 +64553,23 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 total: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -64594,208 +64578,203 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>66.02 trim3: parent 248.278,31 != sum(children) 1.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>66.02 est2028: parent 61.905,93 != sum(children) 31.072,13 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>66.02 total: parent 711.269,55 != sum(children) 30.343,87 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 56.48 total: still inconsistent — UNRESOLVED</t>
+          <t>66.02 est2027: parent 62.026,83 != sum(children) 31.132,81 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 56.48 trim1: still inconsistent — UNRESOLVED</t>
+          <t>66.02 trim4: parent 182.111,94 != sum(children) 1.855,81 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 est2027: still inconsistent — UNRESOLVED</t>
+          <t>66.02 trim2: parent 273.726,30 != sum(children) 27.488,06 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -64804,281 +64783,276 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 est2028: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 total: still inconsistent — UNRESOLVED</t>
+          <t>56 trim2: parent 0,00 != sum(children) 5.886,22 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>56 total: parent 0,00 != sum(children) 15.557,72 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>56 trim3: parent 0,00 != sum(children) 5.600,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>56 trim4: parent 0,00 != sum(children) 4.071,50 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>67.02 trim3: parent 25.462,29 != sum(children) 16.575,29 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LLM re-read 10 rows for 20 total: still inconsistent — UNRESOLVED</t>
+          <t>67.02 est2028: parent 111.390,99 != sum(children) 76.580,04 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LLM re-read 10 rows for 20 trim1: still inconsistent — UNRESOLVED</t>
+          <t>67.02 total: parent 102.525,23 != sum(children) 68.530,17 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>LLM re-read 10 rows for 20 trim2: still inconsistent — UNRESOLVED</t>
+          <t>67.02 trim1: parent 24.066,38 != sum(children) 16.883,73 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -65088,207 +65062,207 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 70.02 est2027: sum now consistent — applied</t>
+          <t>67.02 est2027: parent 111.589,00 != sum(children) 76.710,07 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 70.02 est2028: sum now consistent — applied</t>
+          <t>67.02 trim4: parent 18.585,29 != sum(children) 11.657,88 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 70.02 total: sum now consistent — applied</t>
+          <t>67.02 trim2: parent 34.411,27 != sum(children) 23.413,27 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 70.02 trim1: sum now consistent — applied</t>
+          <t>67.02 trim3: parent 25.462,29 != sum(children) 2.643,66 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 70.02 trim2: sum now consistent — applied</t>
+          <t>67.02 est2028: parent 111.390,99 != sum(children) 21.343,71 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 70.02 trim3: sum now consistent — applied</t>
+          <t>67.02 total: parent 102.525,23 != sum(children) 11.077,84 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 70.02 trim4: sum now consistent — applied</t>
+          <t>67.02 trim1: parent 24.066,38 != sum(children) 782,65 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -65298,357 +65272,352 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 74.02 est2027: sum now consistent — applied</t>
+          <t>67.02 est2027: parent 111.589,00 != sum(children) 21.365,87 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 74.02 est2028: sum now consistent — applied</t>
+          <t>67.02 trim4: parent 18.585,29 != sum(children) 643,91 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 74.02 total: sum now consistent — applied</t>
+          <t>67.02 trim2: parent 34.411,27 != sum(children) 7.007,62 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 74.02 trim1: sum now consistent — applied</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>56.48</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 74.02 trim2: sum now consistent — applied</t>
+          <t>56.48 total: parent 2.216,55 != sum(children) 1.282,16 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>56.48</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61 total: still inconsistent — UNRESOLVED</t>
+          <t>56.48 trim1: parent 2.216,55 != sum(children) 1.282,16 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61 trim1: still inconsistent — UNRESOLVED</t>
+          <t>68.02 trim3: parent 22.676,00 != sum(children) 18.549,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61 trim2: still inconsistent — UNRESOLVED</t>
+          <t>68.02 est2028: parent 98.592,34 != sum(children) 83.904,03 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 est2027: still inconsistent — UNRESOLVED</t>
+          <t>68.02 total: parent 91.558,86 != sum(children) 77.250,94 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 est2028: still inconsistent — UNRESOLVED</t>
+          <t>68.02 trim1: parent 23.891,64 != sum(children) 20.054,72 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 total: still inconsistent — UNRESOLVED</t>
+          <t>68.02 est2027: parent 96.233,45 != sum(children) 81.516,44 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>68.02 trim4: parent 19.917,22 != sum(children) 18.312,22 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -65658,284 +65627,279 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>68.02 trim2: parent 25.074,00 != sum(children) 20.335,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>68.02 est2028: parent 98.592,34 != sum(children) 281,60 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>68.02 total: parent 91.558,86 != sum(children) 217,58 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 81.02 est2027: sum now consistent — applied</t>
+          <t>68.02 trim1: parent 23.891,64 != sum(children) -57,42 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 81.02 est2028: sum now consistent — applied</t>
+          <t>68.02 est2027: parent 96.233,45 != sum(children) 282,15 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 81.02 total: sum now consistent — applied</t>
+          <t>68.02 trim2: parent 25.074,00 != sum(children) 275,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>81.02</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 81.02 trim1: sum now consistent — applied</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 81.02 trim2: sum now consistent — applied</t>
+          <t>20 total: parent 3.508,00 != sum(children) 3.503,00 (9 children)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 81.02 trim3: sum now consistent — applied</t>
+          <t>20 trim1: parent 1.157,00 != sum(children) 1.155,00 (9 children)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 81.02 trim4: sum now consistent — applied</t>
+          <t>20 trim2: parent 1.217,00 != sum(children) 1.214,00 (9 children)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -65944,191 +65908,186 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 est2027: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 est2028: still inconsistent — UNRESOLVED</t>
+          <t>70.02 trim3: parent 46.627,57 != sum(children) 4.635,63 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total: still inconsistent — UNRESOLVED</t>
+          <t>70.02 est2028: parent 203.100,93 != sum(children) 127.427,59 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>70.02 total: parent 250.922,28 != sum(children) 106.054,76 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>70.02 trim1: parent 62.963,26 != sum(children) 37.557,42 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>70.02 est2027: parent 188.708,85 != sum(children) 112.887,69 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -66138,157 +66097,147 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>70.02 trim4: parent 63.431,48 != sum(children) 26.182,63 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 56.48 total: sum now consistent — applied</t>
+          <t>70.02 trim2: parent 77.899,97 != sum(children) 37.679,08 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>56.48</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 56.48 trim1: sum now consistent — applied</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>56.48</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 56.48 trim2: sum now consistent — applied</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 56.48 trim3: sum now consistent — applied</t>
+          <t>74.02 est2028: parent 49.837,09 != sum(children) 2.600,96 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 56.48 trim4: sum now consistent — applied</t>
+          <t>74.02 total: parent 76.185,80 != sum(children) 2.480,98 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66304,21 +66253,21 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>07.02 trim2: parent 49.200,00 != sum(children) 91.800,00 (4 children)</t>
+          <t>74.02 trim1: parent 14.865,17 != sum(children) -19,02 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66334,11 +66283,11 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -66348,7 +66297,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>07.02 est2027: parent 154.448,70 != sum(children) 279.917,40 (4 children)</t>
+          <t>74.02 est2027: parent 49.934,42 != sum(children) 2.606,04 (2 children)</t>
         </is>
       </c>
     </row>
@@ -66364,51 +66313,46 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>07.02 trim1: parent 36.155,00 != sum(children) 60.485,00 (4 children)</t>
+          <t>74.02 trim2: parent 39.362,79 != sum(children) 2.500,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>07.02</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>07.02 total: parent 147.900,00 != sum(children) 268.200,00 (4 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -66424,21 +66368,21 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>07.02 est2028: parent 154.098,00 != sum(children) 279.296,00 (4 children)</t>
+          <t>61 trim2: parent 25.075,79 != sum(children) 4.002,88 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66454,21 +66398,21 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>07.02 trim3: parent 45.445,00 != sum(children) 85.015,00 (4 children)</t>
+          <t>61 total: parent 27.575,79 != sum(children) 4.402,88 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66484,21 +66428,21 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>07.02 trim4: parent 17.100,00 != sum(children) 30.900,00 (4 children)</t>
+          <t>61 trim1: parent 2.500,00 != sum(children) 400,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66514,16 +66458,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>07.02.02</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -66539,21 +66483,21 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>36.02 trim2: parent 31.952,78 != sum(children) 9.500,00 (2 children)</t>
+          <t>80.02 trim3: parent 3.900,00 != sum(children) 207.229,62 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66569,21 +66513,21 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>36.02 est2027: parent 87.356,57 != sum(children) 30.352,16 (2 children)</t>
+          <t>80.02 est2028: parent 829,44 != sum(children) 522.083,79 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66599,21 +66543,21 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>36.02 trim1: parent 9.889,07 != sum(children) 1.300,00 (2 children)</t>
+          <t>80.02 total: parent 11.659,31 != sum(children) 823.479,26 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66629,21 +66573,21 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>36.02 total: parent 85.142,85 != sum(children) 29.583,00 (2 children)</t>
+          <t>80.02 trim1: parent 17,00 != sum(children) 235.276,56 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66659,21 +66603,21 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>36.02 est2028: parent 87.186,28 != sum(children) 30.292,99 (2 children)</t>
+          <t>80.02 est2027: parent 831,06 != sum(children) 509.143,18 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66689,21 +66633,21 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>36.02 trim3: parent 27.788,00 != sum(children) 10.500,00 (2 children)</t>
+          <t>80.02 trim4: parent 3.693,00 != sum(children) 156.629,81 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66719,21 +66663,21 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>36.02 trim4: parent 15.513,00 != sum(children) 8.283,00 (2 children)</t>
+          <t>80.02 trim2: parent 4.049,31 != sum(children) 224.343,27 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66749,21 +66693,21 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>42.02.89</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>42.02.89 trim2: parent 76.097,50 != sum(children) 62.138,27 (2 children)</t>
+          <t>80.02 trim3: parent 3.900,00 != sum(children) 400,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66779,21 +66723,21 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>42.02.89</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>42.02.89 trim1: parent 65.499,92 != sum(children) 55.099,92 (2 children)</t>
+          <t>80.02 est2028: parent 829,44 != sum(children) 812,03 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66809,11 +66753,11 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>42.02.89</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -66823,7 +66767,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>42.02.89 total: parent 288.518,44 != sum(children) 243.443,98 (2 children)</t>
+          <t>80.02 total: parent 11.659,31 != sum(children) 793,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66839,21 +66783,21 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>42.02.89</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>42.02.89 trim3: parent 76.285,09 != sum(children) 65.538,64 (2 children)</t>
+          <t>80.02 est2027: parent 831,06 != sum(children) 813,62 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66869,11 +66813,11 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>42.02.89</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -66883,7 +66827,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>42.02.89 trim4: parent 70.635,93 != sum(children) 60.667,15 (2 children)</t>
+          <t>80.02 trim4: parent 3.693,00 != sum(children) 193,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -66899,11 +66843,11 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -66913,37 +66857,32 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>50.02 trim2: parent 812.224,86 != sum(children) 133.035,68 (3 children)</t>
+          <t>80.02 trim2: parent 4.049,31 != sum(children) 200,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>50.02</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>50.02 est2027: parent 1.252.122,26 != sum(children) 325.235,16 (3 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -66959,21 +66898,21 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>50.02 trim1: parent 424.897,27 != sum(children) 146.740,65 (3 children)</t>
+          <t>81.02 trim3: parent 93.025,50 != sum(children) 61.537,50 (3 children)</t>
         </is>
       </c>
     </row>
@@ -66989,21 +66928,21 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>50.02 total: parent 2.532.346,92 != sum(children) 439.188,61 (3 children)</t>
+          <t>81.02 est2028: parent 160.514,14 != sum(children) 31.996,80 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67019,21 +66958,21 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>50.02 est2028: parent 1.275.702,68 != sum(children) 353.333,21 (3 children)</t>
+          <t>81.02 total: parent 312.794,97 != sum(children) 177.524,13 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67049,21 +66988,21 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>50.02 trim3: parent 698.524,10 != sum(children) 104.549,12 (3 children)</t>
+          <t>81.02 trim1: parent 111.864,72 != sum(children) 94.395,79 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67079,21 +67018,21 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>50.02 trim4: parent 596.700,69 != sum(children) 54.863,16 (3 children)</t>
+          <t>81.02 est2027: parent 160.788,57 != sum(children) 32.000,70 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67109,21 +67048,21 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>20 trim2: parent 4.098,00 != sum(children) 3.948,00 (9 children)</t>
+          <t>81.02 trim4: parent 38.817,50 != sum(children) 987,50 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67139,81 +67078,71 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>20 trim1: parent 4.019,00 != sum(children) 3.849,00 (9 children)</t>
+          <t>81.02 trim2: parent 69.087,25 != sum(children) 20.603,34 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>20 total: parent 15.911,00 != sum(children) 15.411,00 (9 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>20 trim3: parent 4.039,00 != sum(children) 3.889,00 (9 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -67229,71 +67158,81 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>20 trim4: parent 3.755,00 != sum(children) 3.725,00 (9 children)</t>
+          <t>84.02 trim2: parent 151.206,71 != sum(children) 1.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>84.02 total: parent 499.024,98 != sum(children) 2.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>84.02 trim3: parent 110.304,12 != sum(children) 1.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -67309,21 +67248,21 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>10.01 trim2: parent 1.013,00 != sum(children) 985,00 (4 children)</t>
+          <t>84.02 trim3: parent 110.304,12 != sum(children) 28.394,12 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67339,21 +67278,21 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>10.01 trim1: parent 1.021,00 != sum(children) 993,00 (4 children)</t>
+          <t>84.02 est2028: parent 360.740,21 != sum(children) 124.714,06 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67369,11 +67308,11 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -67383,7 +67322,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>10.01 total: parent 3.959,20 != sum(children) 3.847,20 (4 children)</t>
+          <t>84.02 total: parent 499.024,98 != sum(children) 98.149,34 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67399,21 +67338,21 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>trim3</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>10.01 trim3: parent 1.006,00 != sum(children) 978,00 (4 children)</t>
+          <t>84.02 trim1: parent 123.394,84 != sum(children) 13.894,84 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67429,71 +67368,81 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>10.01 trim4: parent 919,20 != sum(children) 891,20 (4 children)</t>
+          <t>84.02 est2027: parent 347.523,55 != sum(children) 111.036,41 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>84.02 trim4: parent 114.119,31 != sum(children) 22.379,31 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>84.02 trim2: parent 151.206,71 != sum(children) 33.481,07 (2 children)</t>
         </is>
       </c>
     </row>
@@ -67509,7 +67458,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -67525,50 +67474,60 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>56.48</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>56.48 trim3: parent 0,00 != sum(children) 25.060,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>56.48</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>56.48 total: parent 0,00 != sum(children) 113.474,29 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67584,21 +67543,21 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>56.48</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>trim2</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>67.02 trim2: parent 34.411,27 != sum(children) 23.413,27 (3 children)</t>
+          <t>56.48 trim1: parent 0,00 != sum(children) 16.040,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67614,21 +67573,21 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>56.48</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>67.02 est2027: parent 111.589,00 != sum(children) 76.710,07 (3 children)</t>
+          <t>56.48 trim4: parent 0,00 != sum(children) 42.040,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -67644,28 +67603,28 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>56.48</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>trim1</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>67.02 trim1: parent 24.066,38 != sum(children) 16.883,73 (3 children)</t>
+          <t>56.48 trim2: parent 0,00 != sum(children) 30.334,29 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -67674,58 +67633,48 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.02</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>67.02 total: parent 102.525,23 != sum(children) 68.530,17 (3 children)</t>
+          <t>code 03.00.02 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>07.02.02</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>67.02 est2028: parent 111.390,99 != sum(children) 76.580,04 (3 children)</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -67734,28 +67683,23 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>10.00.02</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>67.02 trim3: parent 25.462,29 != sum(children) 16.575,29 (3 children)</t>
+          <t>code 10.00.02 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -67764,28 +67708,23 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>29.00.02</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>67.02 trim4: parent 18.585,29 != sum(children) 11.657,88 (3 children)</t>
+          <t>code 29.00.02 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -67794,28 +67733,23 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>67.02 trim2: parent 34.411,27 != sum(children) 7.007,62 (1 children)</t>
+          <t>code 30.00.02 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -67824,28 +67758,23 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>33.00.02</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>67.02 est2027: parent 111.589,00 != sum(children) 21.365,87 (1 children)</t>
+          <t>code 33.00.02 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -67854,28 +67783,23 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>41.00.02</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>67.02 trim1: parent 24.066,38 != sum(children) 782,65 (1 children)</t>
+          <t>code 41.00.02 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -67884,111 +67808,91 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>42.00.02</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>67.02 total: parent 102.525,23 != sum(children) 11.077,84 (1 children)</t>
+          <t>code 42.00.02 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>67.02 est2028: parent 111.390,99 != sum(children) 21.343,71 (1 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>67.02 trim3: parent 25.462,29 != sum(children) 2.643,66 (1 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>67.02 trim4: parent 18.585,29 != sum(children) 643,91 (1 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -68004,7 +67908,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -68020,2188 +67924,348 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>56.48</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>56.48 trim1: parent 2.216,55 != sum(children) 1.282,16 (2 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>56.48</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>56.48 total: parent 2.216,55 != sum(children) 1.282,16 (2 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>68.02 trim2: parent 25.074,00 != sum(children) 20.335,00 (3 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>68.02 est2027: parent 96.233,45 != sum(children) 81.516,44 (3 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>68.02 trim1: parent 23.891,64 != sum(children) 20.054,72 (3 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>68.02 total: parent 91.558,86 != sum(children) 77.250,94 (3 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>68.02 est2028: parent 98.592,34 != sum(children) 83.904,03 (3 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>68.02 trim3: parent 22.676,00 != sum(children) 18.549,00 (3 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>68.02 trim4: parent 19.917,22 != sum(children) 18.312,22 (3 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>68.02 est2027: parent 96.233,45 != sum(children) 282,15 (2 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>68.02 trim1: parent 23.891,64 != sum(children) -57,42 (2 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>68.02 total: parent 91.558,86 != sum(children) 217,58 (2 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>68.02 est2028: parent 98.592,34 != sum(children) 281,60 (2 children)</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
-        <is>
-          <t>68.02 trim2: parent 25.074,00 != sum(children) 275,00 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>17</v>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>17</v>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>20 trim2: parent 1.217,00 != sum(children) 1.214,00 (9 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C202" t="n">
-        <v>17</v>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>20 trim1: parent 1.157,00 != sum(children) 1.155,00 (9 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
-        <v>17</v>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>20 total: parent 3.508,00 != sum(children) 3.503,00 (9 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>18</v>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
-        <v>19</v>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
-        <v>21</v>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>21</v>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>21</v>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>61 trim1: parent 2.500,00 != sum(children) 400,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>21</v>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>61 total: parent 27.575,79 != sum(children) 4.402,88 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>21</v>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>61 trim2: parent 25.075,79 != sum(children) 4.002,88 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>22</v>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>22</v>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>80.02 trim2: parent 4.049,31 != sum(children) 224.343,27 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>22</v>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>est2027</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>80.02 est2027: parent 831,06 != sum(children) 509.143,18 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>22</v>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>80.02 trim1: parent 17,00 != sum(children) 235.276,56 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v>22</v>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>80.02 total: parent 11.659,31 != sum(children) 823.479,26 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B216" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C216" t="n">
-        <v>22</v>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>est2028</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>80.02 est2028: parent 829,44 != sum(children) 522.083,79 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C217" t="n">
-        <v>22</v>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>trim3</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>80.02 trim3: parent 3.900,00 != sum(children) 207.229,62 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C218" t="n">
-        <v>22</v>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>trim4</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>80.02 trim4: parent 3.693,00 != sum(children) 156.629,81 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C219" t="n">
-        <v>22</v>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>80.02 trim2: parent 4.049,31 != sum(children) 200,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C220" t="n">
-        <v>22</v>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>est2027</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>80.02 est2027: parent 831,06 != sum(children) 813,62 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C221" t="n">
-        <v>22</v>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>80.02 total: parent 11.659,31 != sum(children) 793,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C222" t="n">
-        <v>22</v>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>est2028</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>80.02 est2028: parent 829,44 != sum(children) 812,03 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B223" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C223" t="n">
-        <v>22</v>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>trim3</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>80.02 trim3: parent 3.900,00 != sum(children) 400,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C224" t="n">
-        <v>22</v>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>trim4</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>80.02 trim4: parent 3.693,00 != sum(children) 193,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C225" t="n">
-        <v>22</v>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C226" t="n">
-        <v>23</v>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C227" t="n">
-        <v>24</v>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C228" t="n">
-        <v>24</v>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>84.02 total: parent 499.024,98 != sum(children) 2.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C229" t="n">
-        <v>24</v>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>trim3</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>84.02 trim3: parent 110.304,12 != sum(children) 1.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C230" t="n">
-        <v>24</v>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>84.02 trim2: parent 151.206,71 != sum(children) 1.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C231" t="n">
-        <v>24</v>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>84.02 trim2: parent 151.206,71 != sum(children) 33.481,07 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C232" t="n">
-        <v>24</v>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>est2027</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>84.02 est2027: parent 347.523,55 != sum(children) 111.036,41 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C233" t="n">
-        <v>24</v>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>trim1</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>84.02 trim1: parent 123.394,84 != sum(children) 13.894,84 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C234" t="n">
-        <v>24</v>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>84.02 total: parent 499.024,98 != sum(children) 98.149,34 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B235" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C235" t="n">
-        <v>24</v>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>est2028</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>84.02 est2028: parent 360.740,21 != sum(children) 124.714,06 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C236" t="n">
-        <v>24</v>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>trim3</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>84.02 trim3: parent 110.304,12 != sum(children) 28.394,12 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B237" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C237" t="n">
-        <v>24</v>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>trim4</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>84.02 trim4: parent 114.119,31 != sum(children) 22.379,31 (2 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
-        <v>24</v>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B239" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C239" t="n">
-        <v>27</v>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>03.00.02</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>code 03.00.02 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C240" t="n">
-        <v>27</v>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>07.02.02</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>duplicate of p1 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C241" t="n">
-        <v>27</v>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>10.00.02</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>code 10.00.02 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C242" t="n">
-        <v>28</v>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>29.00.02</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>code 29.00.02 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C243" t="n">
-        <v>28</v>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>30.00.02</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>code 30.00.02 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C244" t="n">
-        <v>28</v>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>33.00.02</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>code 33.00.02 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C245" t="n">
-        <v>29</v>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>41.00.02</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>code 41.00.02 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C246" t="n">
-        <v>29</v>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>42.00.02</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>code 42.00.02 (expense_functional) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C247" t="n">
-        <v>33</v>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>33</v>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C249" t="n">
-        <v>34</v>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
-        <v>35</v>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
-        <v>36</v>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C252" t="n">
-        <v>38</v>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
-        <v>39</v>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C254" t="n">
-        <v>41</v>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C255" t="n">
-        <v>43</v>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
-        <v>44</v>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C257" t="n">
-        <v>45</v>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
-        <v>47</v>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>47</v>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C260" t="n">
-        <v>48</v>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C261" t="n">
-        <v>48</v>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C262" t="n">
-        <v>49</v>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C263" t="n">
-        <v>50</v>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>50</v>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
         <is>
           <t>duplicate of p5 with different values</t>
         </is>
@@ -70218,7 +68282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -70240,7 +68304,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -70250,72 +68314,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1342</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1284</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6305</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5916</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>94.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4a4cd58429b393d390b378b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5789dec3c90122da33559f7b31142cf38241b73eb082fbaa0aade7af5faca7f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL LOCAL PE ANUL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-52, 1366 linii</t>
         </is>
